--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.008417747105701008</v>
       </c>
       <c r="C2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>14380670</v>
+        <v>4605228</v>
       </c>
       <c r="L2" t="n">
-        <v>8969326</v>
+        <v>2739716</v>
       </c>
       <c r="M2" t="n">
-        <v>2382586</v>
+        <v>687186</v>
       </c>
       <c r="N2" t="n">
-        <v>154351</v>
+        <v>34785</v>
       </c>
       <c r="O2" t="n">
-        <v>1380862</v>
+        <v>415219</v>
       </c>
       <c r="P2" t="n">
-        <v>536207</v>
+        <v>165713</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999568462371826</v>
+        <v>0.9999385476112366</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9575325846672058</v>
+        <v>0.917241096496582</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8959184885025024</v>
+        <v>0.8188014030456543</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8785586357116699</v>
+        <v>0.7760876417160034</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7357580661773682</v>
+        <v>0.5045765042304993</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9054132103919983</v>
+        <v>0.8203493356704712</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9367108345031738</v>
+        <v>0.8770203590393066</v>
       </c>
       <c r="X2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="AG2" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AH2" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AI2" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566799402236938</v>
+        <v>0.9565494656562805</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112439155578613</v>
+        <v>0.9113017320632935</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581776022911072</v>
+        <v>0.8579359650611877</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626315712928772</v>
+        <v>0.6623888611793518</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020464420318604</v>
+        <v>0.9020065665245056</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002018670822238358</v>
       </c>
       <c r="C3" t="n">
-        <v>556</v>
+        <v>194</v>
       </c>
       <c r="D3" t="n">
-        <v>14380670</v>
+        <v>4605228</v>
       </c>
       <c r="E3" t="n">
-        <v>713528</v>
+        <v>418729</v>
       </c>
       <c r="F3" t="n">
-        <v>5606</v>
+        <v>3755</v>
       </c>
       <c r="G3" t="n">
-        <v>1087</v>
+        <v>605</v>
       </c>
       <c r="H3" t="n">
-        <v>269</v>
+        <v>182</v>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>30049049</v>
+        <v>10016234</v>
       </c>
       <c r="K3" t="n">
-        <v>33249267</v>
+        <v>10885387</v>
       </c>
       <c r="L3" t="n">
-        <v>38167945</v>
+        <v>12459116</v>
       </c>
       <c r="M3" t="n">
-        <v>45864174</v>
+        <v>15199217</v>
       </c>
       <c r="N3" t="n">
-        <v>48666168</v>
+        <v>16206317</v>
       </c>
       <c r="O3" t="n">
-        <v>47317608</v>
+        <v>15729492</v>
       </c>
       <c r="P3" t="n">
-        <v>48372725</v>
+        <v>16113062</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9522526264190674</v>
+        <v>0.9157885909080505</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9172157049179077</v>
+        <v>0.839324414730072</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8523585796356201</v>
+        <v>0.7372291088104248</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5776652693748474</v>
+        <v>0.3902770280838013</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9043352007865906</v>
+        <v>0.8154692649841309</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9247403740882874</v>
+        <v>0.8572795987129211</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="Z3" t="n">
-        <v>593526</v>
+        <v>197896</v>
       </c>
       <c r="AA3" t="n">
-        <v>25572</v>
+        <v>8540</v>
       </c>
       <c r="AB3" t="n">
-        <v>20336</v>
+        <v>6789</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30049866</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>33232195</v>
+        <v>11082162</v>
       </c>
       <c r="AG3" t="n">
-        <v>38343158</v>
+        <v>12776309</v>
       </c>
       <c r="AH3" t="n">
-        <v>45797268</v>
+        <v>15265103</v>
       </c>
       <c r="AI3" t="n">
-        <v>48631528</v>
+        <v>16210402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47312358</v>
+        <v>15770546</v>
       </c>
       <c r="AK3" t="n">
-        <v>48369192</v>
+        <v>16123045</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576433300971985</v>
+        <v>0.957583487033844</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.910033106803894</v>
+        <v>0.9099507331848145</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8577702045440674</v>
+        <v>0.8576524257659912</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.662115752696991</v>
+        <v>0.6619057655334473</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016677737236023</v>
+        <v>0.9016434550285339</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03186393749853683</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>599943</v>
+        <v>392274</v>
       </c>
       <c r="E4" t="n">
-        <v>8969326</v>
+        <v>2739716</v>
       </c>
       <c r="F4" t="n">
-        <v>198410</v>
+        <v>123290</v>
       </c>
       <c r="G4" t="n">
-        <v>4195</v>
+        <v>3102</v>
       </c>
       <c r="H4" t="n">
-        <v>6605</v>
+        <v>5484</v>
       </c>
       <c r="I4" t="n">
-        <v>381</v>
+        <v>326</v>
       </c>
       <c r="J4" t="n">
-        <v>817</v>
+        <v>388</v>
       </c>
       <c r="K4" t="n">
-        <v>637795</v>
+        <v>415511</v>
       </c>
       <c r="L4" t="n">
-        <v>1041993</v>
+        <v>606292</v>
       </c>
       <c r="M4" t="n">
-        <v>329340</v>
+        <v>198263</v>
       </c>
       <c r="N4" t="n">
-        <v>55434</v>
+        <v>34154</v>
       </c>
       <c r="O4" t="n">
-        <v>144256</v>
+        <v>90930</v>
       </c>
       <c r="P4" t="n">
-        <v>36229</v>
+        <v>23237</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999784231185913</v>
+        <v>0.9999693036079407</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9548852443695068</v>
+        <v>0.9165142774581909</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9064420461654663</v>
+        <v>0.8289358615875244</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8652603626251221</v>
+        <v>0.7561594843864441</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6471970677375793</v>
+        <v>0.4401270151138306</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9048739075660706</v>
+        <v>0.8179020285606384</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9306871294975281</v>
+        <v>0.8670376539230347</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>611398</v>
+        <v>204218</v>
       </c>
       <c r="Z4" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AA4" t="n">
-        <v>248302</v>
+        <v>83015</v>
       </c>
       <c r="AB4" t="n">
-        <v>16438</v>
+        <v>5489</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>654867</v>
+        <v>218736</v>
       </c>
       <c r="AG4" t="n">
-        <v>866780</v>
+        <v>289099</v>
       </c>
       <c r="AH4" t="n">
-        <v>396246</v>
+        <v>132377</v>
       </c>
       <c r="AI4" t="n">
-        <v>90074</v>
+        <v>30069</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149506</v>
+        <v>49876</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571613669395447</v>
+        <v>0.9570662379264832</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106380939483643</v>
+        <v>0.910625696182251</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579738140106201</v>
+        <v>0.8577942252159119</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6623735427856445</v>
+        <v>0.6621472835540771</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018570184707642</v>
+        <v>0.9018250107765198</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D5" t="n">
-        <v>22123</v>
+        <v>13707</v>
       </c>
       <c r="E5" t="n">
-        <v>284217</v>
+        <v>163818</v>
       </c>
       <c r="F5" t="n">
-        <v>2382586</v>
+        <v>687186</v>
       </c>
       <c r="G5" t="n">
-        <v>24627</v>
+        <v>15049</v>
       </c>
       <c r="H5" t="n">
-        <v>78768</v>
+        <v>49971</v>
       </c>
       <c r="I5" t="n">
-        <v>2794</v>
+        <v>2220</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>721068</v>
+        <v>423474</v>
       </c>
       <c r="L5" t="n">
-        <v>809536</v>
+        <v>524476</v>
       </c>
       <c r="M5" t="n">
-        <v>412700</v>
+        <v>244934</v>
       </c>
       <c r="N5" t="n">
-        <v>112847</v>
+        <v>54344</v>
       </c>
       <c r="O5" t="n">
-        <v>146074</v>
+        <v>93959</v>
       </c>
       <c r="P5" t="n">
-        <v>43639</v>
+        <v>27588</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999833106994629</v>
+        <v>0.9999762177467346</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9722617864608765</v>
+        <v>0.9486218094825745</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9622050523757935</v>
+        <v>0.9307534694671631</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9848528504371643</v>
+        <v>0.972859263420105</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9965649247169495</v>
+        <v>0.9945805072784424</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9940735697746277</v>
+        <v>0.9886776804924011</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9983696937561035</v>
+        <v>0.9968875646591187</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>23984</v>
+        <v>8010</v>
       </c>
       <c r="Z5" t="n">
-        <v>254565</v>
+        <v>84966</v>
       </c>
       <c r="AA5" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AB5" t="n">
-        <v>29795</v>
+        <v>9941</v>
       </c>
       <c r="AC5" t="n">
-        <v>87330</v>
+        <v>29135</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>639659</v>
+        <v>213300</v>
       </c>
       <c r="AG5" t="n">
-        <v>879774</v>
+        <v>293938</v>
       </c>
       <c r="AH5" t="n">
-        <v>397573</v>
+        <v>132685</v>
       </c>
       <c r="AI5" t="n">
-        <v>90282</v>
+        <v>30134</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150147</v>
+        <v>50081</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735750555992126</v>
+        <v>0.9735427498817444</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643478989601135</v>
+        <v>0.9642956852912903</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837958812713623</v>
+        <v>0.9837679862976074</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963183999061584</v>
+        <v>0.9963132739067078</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938832521438599</v>
+        <v>0.9938787817955017</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983758926391602</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>15636</v>
+        <v>9472</v>
       </c>
       <c r="E6" t="n">
-        <v>38127</v>
+        <v>18475</v>
       </c>
       <c r="F6" t="n">
-        <v>40246</v>
+        <v>16005</v>
       </c>
       <c r="G6" t="n">
-        <v>154351</v>
+        <v>34785</v>
       </c>
       <c r="H6" t="n">
-        <v>17690</v>
+        <v>9683</v>
       </c>
       <c r="I6" t="n">
-        <v>1103</v>
+        <v>693</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19318</v>
+        <v>6452</v>
       </c>
       <c r="Z6" t="n">
-        <v>16016</v>
+        <v>5347</v>
       </c>
       <c r="AA6" t="n">
-        <v>32584</v>
+        <v>10875</v>
       </c>
       <c r="AB6" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AC6" t="n">
-        <v>20921</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>5795</v>
+        <v>5034</v>
       </c>
       <c r="F7" t="n">
-        <v>83517</v>
+        <v>54004</v>
       </c>
       <c r="G7" t="n">
-        <v>24768</v>
+        <v>14896</v>
       </c>
       <c r="H7" t="n">
-        <v>1380862</v>
+        <v>415219</v>
       </c>
       <c r="I7" t="n">
-        <v>31929</v>
+        <v>19989</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2430</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>88798</v>
+        <v>29617</v>
       </c>
       <c r="AB7" t="n">
-        <v>22710</v>
+        <v>7585</v>
       </c>
       <c r="AC7" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>326</v>
+        <v>236</v>
       </c>
       <c r="F8" t="n">
-        <v>1561</v>
+        <v>1209</v>
       </c>
       <c r="G8" t="n">
-        <v>757</v>
+        <v>502</v>
       </c>
       <c r="H8" t="n">
-        <v>40924</v>
+        <v>25610</v>
       </c>
       <c r="I8" t="n">
-        <v>536207</v>
+        <v>165713</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
